--- a/templates/GDA-FLC-014_humedad_natural.xlsx
+++ b/templates/GDA-FLC-014_humedad_natural.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeoDelta Líneas\Dropbox\14. GEODELTA\014 FORMATOS ACTUALIZADOS 2026\FORMATOS PARA DIGITAR ACTUALIZADOS 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DCM-04\AppData\Local\Temp\claude\D--Documents-Prototipos-claude-code-interfaz\dc24a8ee-ce81-4bc3-875e-fdda07eddd40\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACED3D1-5226-4AB7-937B-BFF0D33B62AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8AB2D94-9D1A-4125-8280-1E783ECCDD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUIA" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">GUIA!$A$1:$N$38</definedName>
     <definedName name="GFDGSD">[1]L!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1665,19 +1665,171 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1690,7 +1842,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1703,11 +1854,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1720,156 +1866,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,6 +2086,93 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>84298</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>201452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Firma Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7033D5EF-B26E-4005-A17A-76022D4414D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="88188"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5838825" y="7828123"/>
+          <a:ext cx="2495550" cy="974404"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>359945</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>754480</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Firma Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{675AC09E-432F-433A-BACB-0CE455AE023B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9675395" y="7743825"/>
+          <a:ext cx="1956635" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2341,24 +2428,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="172"/>
-      <c r="B1" s="173"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="117" t="s">
+      <c r="A1" s="83"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="118" t="s">
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="119"/>
-      <c r="N1" s="120"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="146"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -2393,24 +2480,24 @@
       <c r="AT1" s="2"/>
     </row>
     <row r="2" spans="1:46" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="176"/>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="121" t="s">
+      <c r="A2" s="84"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="124" t="s">
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="148"/>
+      <c r="L2" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="125"/>
-      <c r="N2" s="126"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -2445,22 +2532,22 @@
       <c r="AT2" s="2"/>
     </row>
     <row r="3" spans="1:46" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="176"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="124" t="s">
+      <c r="A3" s="84"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="148"/>
+      <c r="L3" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="125"/>
-      <c r="N3" s="126"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="153"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -2479,12 +2566,12 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
       <c r="AF3" s="2"/>
-      <c r="AG3" s="134" t="s">
+      <c r="AG3" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="AH3" s="84"/>
-      <c r="AI3" s="84"/>
-      <c r="AJ3" s="84"/>
+      <c r="AH3" s="90"/>
+      <c r="AI3" s="90"/>
+      <c r="AJ3" s="90"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
@@ -2497,22 +2584,22 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="1:46" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="179"/>
-      <c r="B4" s="180"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="135" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="136"/>
-      <c r="N4" s="137"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="129"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -2531,10 +2618,10 @@
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
-      <c r="AG4" s="84"/>
-      <c r="AH4" s="84"/>
-      <c r="AI4" s="84"/>
-      <c r="AJ4" s="84"/>
+      <c r="AG4" s="90"/>
+      <c r="AH4" s="90"/>
+      <c r="AI4" s="90"/>
+      <c r="AJ4" s="90"/>
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
@@ -2548,17 +2635,17 @@
     </row>
     <row r="5" spans="1:46" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="105"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
       <c r="M5" s="6"/>
       <c r="N5" s="7"/>
       <c r="O5" s="2"/>
@@ -2579,10 +2666,10 @@
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
-      <c r="AJ5" s="84"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
@@ -2596,22 +2683,22 @@
     </row>
     <row r="6" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="139"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="138" t="s">
+      <c r="C6" s="109"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="139"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="141"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="111"/>
       <c r="N6" s="8"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -2650,22 +2737,22 @@
     </row>
     <row r="7" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="128"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="127" t="s">
+      <c r="C7" s="114"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="128"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="131"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="119"/>
       <c r="N7" s="10"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -2704,22 +2791,22 @@
     </row>
     <row r="8" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="127" t="s">
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="128"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="131"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="125"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="119"/>
       <c r="N8" s="10"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -2758,19 +2845,19 @@
     </row>
     <row r="9" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="128"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="127" t="s">
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="128"/>
+      <c r="J9" s="114"/>
       <c r="K9" s="11" t="s">
         <v>18</v>
       </c>
@@ -2814,25 +2901,25 @@
     </row>
     <row r="10" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="143" t="s">
+      <c r="B10" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="144" t="s">
+      <c r="C10" s="90"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="145"/>
-      <c r="K10" s="133" t="str">
+      <c r="J10" s="121"/>
+      <c r="K10" s="115" t="str">
         <f>CONCATENATE(L9,," ",M9,"-",F12,"-",B40,H12)</f>
         <v xml:space="preserve"> --</v>
       </c>
-      <c r="L10" s="130"/>
-      <c r="M10" s="131"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="119"/>
       <c r="N10" s="14"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -2871,17 +2958,17 @@
     </row>
     <row r="11" spans="1:46" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="148"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="124"/>
       <c r="M11" s="15"/>
       <c r="N11" s="16"/>
       <c r="O11" s="2"/>
@@ -2919,21 +3006,21 @@
     </row>
     <row r="12" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="138" t="s">
+      <c r="B12" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="139"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="141"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
       <c r="F12" s="17"/>
       <c r="G12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="19"/>
-      <c r="I12" s="150" t="s">
+      <c r="I12" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="139"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="20"/>
       <c r="L12" s="21" t="s">
         <v>26</v>
@@ -2975,20 +3062,20 @@
     </row>
     <row r="13" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="151"/>
-      <c r="H13" s="151"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="151"/>
-      <c r="K13" s="151"/>
-      <c r="L13" s="151"/>
-      <c r="M13" s="152"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="117"/>
       <c r="N13" s="24"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -3120,22 +3207,22 @@
       <c r="AT15" s="2"/>
     </row>
     <row r="16" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="154"/>
-      <c r="K16" s="154"/>
-      <c r="L16" s="154"/>
-      <c r="M16" s="154"/>
-      <c r="N16" s="155"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="88"/>
     </row>
     <row r="17" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="30"/>
@@ -3143,11 +3230,11 @@
     </row>
     <row r="18" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
-      <c r="E18" s="156"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="84"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="90"/>
       <c r="N18" s="31"/>
       <c r="T18" s="32" t="s">
         <v>29</v>
@@ -3159,30 +3246,30 @@
     </row>
     <row r="19" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="30"/>
-      <c r="E19" s="163" t="s">
+      <c r="E19" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="89"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
       <c r="N19" s="31"/>
       <c r="T19" s="30"/>
       <c r="U19" s="31"/>
     </row>
     <row r="20" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30"/>
-      <c r="E20" s="165" t="s">
+      <c r="E20" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="130"/>
-      <c r="G20" s="166"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="104"/>
       <c r="H20" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="157"/>
-      <c r="J20" s="158"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
       <c r="N20" s="31"/>
       <c r="T20" s="36" t="s">
         <v>33</v>
@@ -3191,16 +3278,16 @@
     </row>
     <row r="21" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30"/>
-      <c r="E21" s="165" t="s">
+      <c r="E21" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="130"/>
-      <c r="G21" s="166"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="104"/>
       <c r="H21" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="I21" s="157"/>
-      <c r="J21" s="158"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
       <c r="N21" s="31"/>
       <c r="P21" s="38"/>
       <c r="T21" s="39" t="s">
@@ -3210,56 +3297,56 @@
     </row>
     <row r="22" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="30"/>
-      <c r="E22" s="167" t="s">
+      <c r="E22" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="168"/>
-      <c r="G22" s="169"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="107"/>
       <c r="H22" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="159"/>
-      <c r="J22" s="160"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="94"/>
       <c r="N22" s="31"/>
-      <c r="T22" s="161" t="s">
+      <c r="T22" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="U22" s="162"/>
+      <c r="U22" s="96"/>
     </row>
     <row r="23" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="30"/>
-      <c r="E23" s="85" t="s">
+      <c r="E23" s="162" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="86"/>
-      <c r="G23" s="87"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="99"/>
       <c r="H23" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="88" t="str">
+      <c r="I23" s="163" t="str">
         <f>+IF(I21=0,"",I21-I22)</f>
         <v/>
       </c>
-      <c r="J23" s="89"/>
+      <c r="J23" s="101"/>
       <c r="N23" s="31"/>
       <c r="T23" s="30"/>
       <c r="U23" s="31"/>
     </row>
     <row r="24" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="30"/>
-      <c r="E24" s="90" t="s">
+      <c r="E24" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="91"/>
-      <c r="G24" s="92"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="166"/>
       <c r="H24" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="93" t="str">
+      <c r="I24" s="167" t="str">
         <f>+IF(I20=0,"",(I20-I21)/(I21-I22)*100)</f>
         <v/>
       </c>
-      <c r="J24" s="94"/>
+      <c r="J24" s="168"/>
       <c r="N24" s="31"/>
       <c r="T24" s="44" t="s">
         <v>41</v>
@@ -3277,18 +3364,18 @@
     <row r="26" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="48"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="97"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="170"/>
       <c r="M26" s="49"/>
       <c r="N26" s="50"/>
       <c r="O26" s="49"/>
@@ -3327,19 +3414,19 @@
     <row r="27" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="48"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="176" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="103"/>
-      <c r="E27" s="98" t="s">
+      <c r="D27" s="142"/>
+      <c r="E27" s="171" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="99"/>
-      <c r="G27" s="102" t="s">
+      <c r="F27" s="172"/>
+      <c r="G27" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
       <c r="J27" s="51" t="s">
         <v>47</v>
       </c>
@@ -3385,13 +3472,13 @@
     <row r="28" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
+      <c r="C28" s="177"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="149"/>
+      <c r="H28" s="149"/>
+      <c r="I28" s="149"/>
       <c r="J28" s="53"/>
       <c r="K28" s="54"/>
       <c r="L28" s="55"/>
@@ -3486,21 +3573,21 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="105" t="s">
+      <c r="H30" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="I30" s="84"/>
+      <c r="I30" s="90"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="105" t="s">
+      <c r="K30" s="130" t="s">
         <v>50</v>
       </c>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
       <c r="N30" s="7"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="84"/>
-      <c r="R30" s="84"/>
+      <c r="P30" s="133"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
       <c r="S30" s="57"/>
       <c r="T30" s="58"/>
       <c r="U30" s="56"/>
@@ -3532,14 +3619,14 @@
     </row>
     <row r="31" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
-      <c r="B31" s="108" t="s">
+      <c r="B31" s="178" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -3548,9 +3635,9 @@
       <c r="M31" s="2"/>
       <c r="N31" s="7"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="84"/>
-      <c r="R31" s="84"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="90"/>
       <c r="S31" s="57"/>
       <c r="T31" s="58"/>
       <c r="U31" s="56"/>
@@ -3582,14 +3669,14 @@
     </row>
     <row r="32" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
-      <c r="B32" s="109" t="s">
+      <c r="B32" s="179" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="90"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -3598,18 +3685,18 @@
       <c r="M32" s="2"/>
       <c r="N32" s="7"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="84"/>
-      <c r="R32" s="84"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="90"/>
       <c r="S32" s="61"/>
       <c r="T32" s="62"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="62"/>
-      <c r="Y32" s="112"/>
-      <c r="Z32" s="84"/>
-      <c r="AA32" s="84"/>
+      <c r="Y32" s="133"/>
+      <c r="Z32" s="90"/>
+      <c r="AA32" s="90"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="2"/>
@@ -3632,12 +3719,12 @@
     </row>
     <row r="33" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
-      <c r="G33" s="84"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -3646,18 +3733,18 @@
       <c r="M33" s="2"/>
       <c r="N33" s="7"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="112"/>
-      <c r="Q33" s="84"/>
-      <c r="R33" s="84"/>
+      <c r="P33" s="133"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="90"/>
       <c r="S33" s="61"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
-      <c r="Y33" s="105"/>
-      <c r="Z33" s="84"/>
-      <c r="AA33" s="84"/>
+      <c r="Y33" s="130"/>
+      <c r="Z33" s="90"/>
+      <c r="AA33" s="90"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
@@ -3680,12 +3767,12 @@
     </row>
     <row r="34" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="84"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
       <c r="H34" s="63"/>
       <c r="I34" s="63"/>
       <c r="J34" s="62"/>
@@ -3728,37 +3815,37 @@
     </row>
     <row r="35" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="110" t="s">
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="157" t="s">
         <v>53</v>
       </c>
-      <c r="I35" s="111"/>
+      <c r="I35" s="158"/>
       <c r="J35" s="62"/>
-      <c r="K35" s="110" t="s">
+      <c r="K35" s="157" t="s">
         <v>68</v>
       </c>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
+      <c r="L35" s="158"/>
+      <c r="M35" s="158"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="113"/>
-      <c r="P35" s="84"/>
-      <c r="Q35" s="84"/>
-      <c r="R35" s="84"/>
-      <c r="S35" s="84"/>
-      <c r="T35" s="84"/>
-      <c r="U35" s="84"/>
-      <c r="V35" s="84"/>
-      <c r="W35" s="84"/>
-      <c r="X35" s="84"/>
-      <c r="Y35" s="84"/>
-      <c r="Z35" s="84"/>
-      <c r="AA35" s="84"/>
-      <c r="AB35" s="84"/>
+      <c r="O35" s="155"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="90"/>
+      <c r="U35" s="90"/>
+      <c r="V35" s="90"/>
+      <c r="W35" s="90"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="90"/>
+      <c r="Z35" s="90"/>
+      <c r="AA35" s="90"/>
+      <c r="AB35" s="90"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="2"/>
       <c r="AE35" s="2"/>
@@ -3780,37 +3867,37 @@
     </row>
     <row r="36" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="84"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84"/>
-      <c r="H36" s="105" t="s">
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="I36" s="84"/>
+      <c r="I36" s="90"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="105" t="s">
+      <c r="K36" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="L36" s="84"/>
-      <c r="M36" s="84"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
       <c r="N36" s="7"/>
-      <c r="O36" s="84"/>
-      <c r="P36" s="84"/>
-      <c r="Q36" s="84"/>
-      <c r="R36" s="84"/>
-      <c r="S36" s="84"/>
-      <c r="T36" s="84"/>
-      <c r="U36" s="84"/>
-      <c r="V36" s="84"/>
-      <c r="W36" s="84"/>
-      <c r="X36" s="84"/>
-      <c r="Y36" s="84"/>
-      <c r="Z36" s="84"/>
-      <c r="AA36" s="84"/>
-      <c r="AB36" s="84"/>
+      <c r="O36" s="90"/>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="90"/>
+      <c r="R36" s="90"/>
+      <c r="S36" s="90"/>
+      <c r="T36" s="90"/>
+      <c r="U36" s="90"/>
+      <c r="V36" s="90"/>
+      <c r="W36" s="90"/>
+      <c r="X36" s="90"/>
+      <c r="Y36" s="90"/>
+      <c r="Z36" s="90"/>
+      <c r="AA36" s="90"/>
+      <c r="AB36" s="90"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="2"/>
       <c r="AE36" s="2"/>
@@ -3832,12 +3919,12 @@
     </row>
     <row r="37" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
       <c r="H37" s="65"/>
       <c r="I37" s="66"/>
       <c r="J37" s="66"/>
@@ -3879,36 +3966,36 @@
       <c r="AT37" s="5"/>
     </row>
     <row r="38" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="115" t="s">
+      <c r="A38" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="116"/>
-      <c r="O38" s="114"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="84"/>
-      <c r="R38" s="84"/>
-      <c r="S38" s="84"/>
-      <c r="T38" s="84"/>
-      <c r="U38" s="84"/>
-      <c r="V38" s="84"/>
-      <c r="W38" s="84"/>
-      <c r="X38" s="84"/>
-      <c r="Y38" s="84"/>
-      <c r="Z38" s="84"/>
-      <c r="AA38" s="84"/>
-      <c r="AB38" s="84"/>
+      <c r="B38" s="149"/>
+      <c r="C38" s="149"/>
+      <c r="D38" s="149"/>
+      <c r="E38" s="149"/>
+      <c r="F38" s="149"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="149"/>
+      <c r="I38" s="149"/>
+      <c r="J38" s="149"/>
+      <c r="K38" s="149"/>
+      <c r="L38" s="149"/>
+      <c r="M38" s="149"/>
+      <c r="N38" s="160"/>
+      <c r="O38" s="156"/>
+      <c r="P38" s="90"/>
+      <c r="Q38" s="90"/>
+      <c r="R38" s="90"/>
+      <c r="S38" s="90"/>
+      <c r="T38" s="90"/>
+      <c r="U38" s="90"/>
+      <c r="V38" s="90"/>
+      <c r="W38" s="90"/>
+      <c r="X38" s="90"/>
+      <c r="Y38" s="90"/>
+      <c r="Z38" s="90"/>
+      <c r="AA38" s="90"/>
+      <c r="AB38" s="90"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
@@ -3932,11 +4019,11 @@
     <row r="40" spans="1:46" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="68"/>
-      <c r="C40" s="83" t="s">
+      <c r="C40" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
       <c r="F40" s="2"/>
       <c r="G40" s="68"/>
       <c r="H40" s="69" t="s">
@@ -4943,40 +5030,30 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:M13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="AG3:AJ5"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G27:I28"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G37"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="O35:AB36"/>
+    <mergeCell ref="O38:AB38"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="H36:I36"/>
     <mergeCell ref="P30:R30"/>
     <mergeCell ref="P31:R31"/>
     <mergeCell ref="P32:R32"/>
@@ -4993,30 +5070,40 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:H8"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="O35:AB36"/>
-    <mergeCell ref="O38:AB38"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G27:I28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G37"/>
-    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="AG3:AJ5"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:M13"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="C28:F28">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
@@ -5098,11 +5185,11 @@
       <c r="E4" s="72"/>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="170" t="s">
+      <c r="C5" s="180" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="73" t="s">
